--- a/results/Case2/results-DBs/panel_data_4plots.xlsx
+++ b/results/Case2/results-DBs/panel_data_4plots.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Panels" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="All_Panels" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Panel_A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Panel_B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Panel_C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Panel_D" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -567,108 +568,110 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.44</v>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Panel B</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Panel B</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Recall</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SelenzymRF</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SelenzymRF</t>
+          <t>SiMMER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="C14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.68</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="E14" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SiMMER</t>
+          <t>Theia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="D15" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="E15" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Theia</t>
+          <t>BEC-Pred</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="D16" t="n">
         <v>0.79</v>
@@ -677,300 +680,228 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BEC-Pred</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Panel C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SelenzymRF</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.78</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.79</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Panel C</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SiMMER</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SelenzymRF</t>
+          <t>Theia</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C23" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>BEC-Pred</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Panel D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SelenzymRF</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>SiMMER</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="B30" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="C30" t="n">
         <v>0.72</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="D30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Theia</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BEC-Pred</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Panel D</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>MCC</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SelenzymRF</t>
+          <t>BEC-Pred</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.74</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SiMMER</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Theia</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BEC-Pred</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1001,6 +932,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1102,25 +1034,6 @@
       </c>
       <c r="E7" t="n">
         <v>0.82</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1151,6 +1064,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1252,25 +1166,6 @@
       </c>
       <c r="E7" t="n">
         <v>0.78</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1301,6 +1196,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1338,13 +1234,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="5">
@@ -1354,16 +1250,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="C5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="D5" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="E5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="6">
@@ -1373,16 +1269,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C6" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="D6" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7">
@@ -1402,25 +1298,6 @@
       </c>
       <c r="E7" t="n">
         <v>0.82</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -1434,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1328,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1491,10 +1369,10 @@
         <v>0.74</v>
       </c>
       <c r="D4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="5">
@@ -1507,13 +1385,13 @@
         <v>0.91</v>
       </c>
       <c r="C5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.74</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.92</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="6">
@@ -1526,13 +1404,13 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="D6" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1545,32 +1423,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="E7" t="n">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CLAIRE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
